--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K352"/>
+  <dimension ref="A1:K356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11891,12 +11891,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>GT8</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>8a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -11948,12 +11948,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>GT8</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>8a</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11961,7 +11961,11 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr"/>
@@ -11969,6 +11973,136 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
     </row>
+    <row r="353"/>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="B354" s="1" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>Subtype</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="E354" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="F354" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="G354" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="H354" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="I354" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="J354" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="K354" s="1" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>NS5B</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>GT8</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>8a</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>NS5B</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>GT8</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>8a</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K356"/>
+  <dimension ref="A1:L356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -431,6 +431,7 @@
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -476,6 +477,11 @@
       <c r="K2" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,13 +561,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -606,6 +605,11 @@
       <c r="K6" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -685,13 +689,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9"/>
     <row r="10">
@@ -736,6 +733,11 @@
       <c r="K10" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -815,17 +817,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <r>
+            <t>N316C</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>72</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="13"/>
     <row r="14">
@@ -870,6 +879,11 @@
       <c r="K14" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -949,17 +963,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <r>
+            <t>N316C</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>72</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="17"/>
     <row r="18">
@@ -1004,6 +1025,11 @@
       <c r="K18" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1083,13 +1109,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21"/>
     <row r="22">
@@ -1134,6 +1153,11 @@
       <c r="K22" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1213,17 +1237,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <r>
+            <t>N206K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>50</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="25"/>
     <row r="26">
@@ -1268,6 +1299,11 @@
       <c r="K26" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1347,17 +1383,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <r>
+            <t>N206K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>60</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="29"/>
     <row r="30">
@@ -1402,6 +1445,11 @@
       <c r="K30" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1481,13 +1529,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33"/>
     <row r="34">
@@ -1532,6 +1573,11 @@
       <c r="K34" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1611,13 +1657,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37"/>
     <row r="38">
@@ -1662,6 +1701,11 @@
       <c r="K38" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1741,13 +1785,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41"/>
     <row r="42">
@@ -1792,6 +1829,11 @@
       <c r="K42" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1871,13 +1913,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45"/>
     <row r="46">
@@ -1922,6 +1957,11 @@
       <c r="K46" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2001,13 +2041,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -2052,6 +2085,11 @@
       <c r="K50" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2131,13 +2169,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54">
@@ -2182,6 +2213,11 @@
       <c r="K54" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2261,13 +2297,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57"/>
     <row r="58">
@@ -2312,6 +2341,11 @@
       <c r="K58" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2391,13 +2425,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61"/>
     <row r="62">
@@ -2442,6 +2469,11 @@
       <c r="K62" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2526,12 +2558,19 @@
           <t>T</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <r>
+            <t>A150T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>43</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="65"/>
     <row r="66">
@@ -2576,6 +2615,11 @@
       <c r="K66" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L66" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2655,13 +2699,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69"/>
     <row r="70">
@@ -2706,6 +2743,11 @@
       <c r="K70" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L70" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2785,13 +2827,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73"/>
     <row r="74">
@@ -2836,6 +2871,11 @@
       <c r="K74" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L74" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2920,12 +2960,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <r>
+            <t>T150A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>86</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="77"/>
     <row r="78">
@@ -2970,6 +3017,11 @@
       <c r="K78" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L78" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3049,13 +3101,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81"/>
     <row r="82">
@@ -3100,6 +3145,11 @@
       <c r="K82" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3179,13 +3229,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85"/>
     <row r="86">
@@ -3230,6 +3273,11 @@
       <c r="K86" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3314,16 +3362,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <r>
+            <t>T150A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>G206K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="89"/>
     <row r="90">
@@ -3368,6 +3436,11 @@
       <c r="K90" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L90" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3447,17 +3520,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <r>
+            <t>R206K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="93"/>
     <row r="94">
@@ -3502,6 +3582,11 @@
       <c r="K94" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L94" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3586,12 +3671,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <r>
+            <t>T150S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>50</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="97"/>
     <row r="98">
@@ -3636,6 +3728,11 @@
       <c r="K98" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L98" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3715,13 +3812,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101"/>
     <row r="102">
@@ -3766,6 +3856,11 @@
       <c r="K102" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L102" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3845,13 +3940,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105"/>
     <row r="106">
@@ -3896,6 +3984,11 @@
       <c r="K106" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L106" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3975,13 +4068,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109"/>
     <row r="110">
@@ -4026,6 +4112,11 @@
       <c r="K110" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4105,13 +4196,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113"/>
     <row r="114">
@@ -4156,6 +4240,11 @@
       <c r="K114" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L114" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4235,13 +4324,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117"/>
     <row r="118">
@@ -4286,6 +4368,11 @@
       <c r="K118" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L118" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4365,13 +4452,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121"/>
     <row r="122">
@@ -4416,6 +4496,11 @@
       <c r="K122" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L122" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4500,16 +4585,36 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <r>
+            <t>T150A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>92</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>E206K</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>92</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="125"/>
     <row r="126">
@@ -4554,6 +4659,11 @@
       <c r="K126" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L126" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4633,13 +4743,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129"/>
     <row r="130">
@@ -4684,6 +4787,11 @@
       <c r="K130" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L130" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4763,13 +4871,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133"/>
     <row r="134">
@@ -4814,6 +4915,11 @@
       <c r="K134" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L134" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4893,17 +4999,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <r>
+            <t>T282S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>99</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="137"/>
     <row r="138">
@@ -4948,6 +5061,11 @@
       <c r="K138" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L138" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5027,13 +5145,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141"/>
     <row r="142">
@@ -5078,6 +5189,11 @@
       <c r="K142" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L142" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5157,13 +5273,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145"/>
     <row r="146">
@@ -5208,6 +5317,11 @@
       <c r="K146" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L146" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5287,13 +5401,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149"/>
     <row r="150">
@@ -5338,6 +5445,11 @@
       <c r="K150" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L150" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5417,13 +5529,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153"/>
     <row r="154">
@@ -5468,6 +5573,11 @@
       <c r="K154" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L154" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5547,13 +5657,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157"/>
     <row r="158">
@@ -5598,6 +5701,11 @@
       <c r="K158" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L158" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5677,17 +5785,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <r>
+            <t>C316N</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>80</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="161"/>
     <row r="162">
@@ -5732,6 +5847,11 @@
       <c r="K162" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L162" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5811,19 +5931,39 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>I</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <r>
+            <t>C316H</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>V321I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>100</t>
+          </r>
         </is>
       </c>
     </row>
@@ -5870,6 +6010,11 @@
       <c r="K166" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L166" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5949,13 +6094,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169"/>
     <row r="170">
@@ -6000,6 +6138,11 @@
       <c r="K170" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L170" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6079,13 +6222,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173"/>
     <row r="174">
@@ -6130,6 +6266,11 @@
       <c r="K174" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L174" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6209,13 +6350,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177"/>
     <row r="178">
@@ -6260,6 +6394,11 @@
       <c r="K178" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L178" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6339,13 +6478,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181"/>
     <row r="182">
@@ -6390,6 +6522,11 @@
       <c r="K182" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L182" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6469,13 +6606,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185"/>
     <row r="186">
@@ -6520,6 +6650,11 @@
       <c r="K186" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L186" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6599,13 +6734,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189"/>
     <row r="190">
@@ -6650,6 +6778,11 @@
       <c r="K190" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L190" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6729,13 +6862,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193"/>
     <row r="194">
@@ -6780,6 +6906,11 @@
       <c r="K194" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L194" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6859,13 +6990,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197"/>
     <row r="198">
@@ -6910,6 +7034,11 @@
       <c r="K198" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L198" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6989,19 +7118,39 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>I</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <r>
+            <t>C316H</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>58</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <t>V321I</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>58</t>
+          </r>
         </is>
       </c>
     </row>
@@ -7048,6 +7197,11 @@
       <c r="K202" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L202" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7127,17 +7281,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <r>
+            <t>A206T</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>67</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="205"/>
     <row r="206">
@@ -7182,6 +7343,11 @@
       <c r="K206" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L206" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7261,13 +7427,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209"/>
     <row r="210">
@@ -7312,6 +7471,11 @@
       <c r="K210" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L210" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7391,17 +7555,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <r>
+            <t>T206A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>75</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="213"/>
     <row r="214">
@@ -7446,6 +7617,11 @@
       <c r="K214" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L214" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7525,13 +7701,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217"/>
     <row r="218">
@@ -7576,6 +7745,11 @@
       <c r="K218" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L218" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7655,13 +7829,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221"/>
     <row r="222">
@@ -7706,6 +7873,11 @@
       <c r="K222" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L222" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7785,13 +7957,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225"/>
     <row r="226">
@@ -7836,6 +8001,11 @@
       <c r="K226" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L226" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7915,13 +8085,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229"/>
     <row r="230">
@@ -7966,6 +8129,11 @@
       <c r="K230" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L230" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8045,13 +8213,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233"/>
     <row r="234">
@@ -8096,6 +8257,11 @@
       <c r="K234" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L234" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8175,13 +8341,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237"/>
     <row r="238">
@@ -8226,6 +8385,11 @@
       <c r="K238" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L238" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8305,13 +8469,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241"/>
     <row r="242">
@@ -8356,6 +8513,11 @@
       <c r="K242" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L242" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8435,13 +8597,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245"/>
     <row r="246">
@@ -8486,6 +8641,11 @@
       <c r="K246" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L246" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8565,13 +8725,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249"/>
     <row r="250">
@@ -8616,6 +8769,11 @@
       <c r="K250" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L250" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8695,13 +8853,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253"/>
     <row r="254">
@@ -8746,6 +8897,11 @@
       <c r="K254" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L254" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8825,13 +8981,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257"/>
     <row r="258">
@@ -8876,6 +9025,11 @@
       <c r="K258" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L258" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8955,13 +9109,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261"/>
     <row r="262">
@@ -9006,6 +9153,11 @@
       <c r="K262" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L262" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9085,17 +9237,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <r>
+            <t>T206A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>60</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="265"/>
     <row r="266">
@@ -9140,6 +9299,11 @@
       <c r="K266" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L266" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9219,13 +9383,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269"/>
     <row r="270">
@@ -9270,6 +9427,11 @@
       <c r="K270" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L270" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9349,13 +9511,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273"/>
     <row r="274">
@@ -9400,6 +9555,11 @@
       <c r="K274" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L274" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9479,17 +9639,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <r>
+            <t>S206R</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>36</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="277"/>
     <row r="278">
@@ -9534,6 +9701,11 @@
       <c r="K278" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L278" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9613,13 +9785,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281"/>
     <row r="282">
@@ -9664,6 +9829,11 @@
       <c r="K282" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L282" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9743,17 +9913,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <r>
+            <t>K206S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>53</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="285"/>
     <row r="286">
@@ -9798,6 +9975,11 @@
       <c r="K286" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L286" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9877,17 +10059,24 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <r>
+            <t>K206S</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>53</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="289"/>
     <row r="290">
@@ -9932,6 +10121,11 @@
       <c r="K290" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L290" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10011,13 +10205,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293"/>
     <row r="294">
@@ -10062,6 +10249,11 @@
       <c r="K294" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L294" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10141,13 +10333,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297"/>
     <row r="298">
@@ -10192,6 +10377,11 @@
       <c r="K298" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L298" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10271,13 +10461,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301"/>
     <row r="302">
@@ -10322,6 +10505,11 @@
       <c r="K302" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L302" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10401,13 +10589,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305"/>
     <row r="306">
@@ -10452,6 +10633,11 @@
       <c r="K306" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L306" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10531,13 +10717,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309"/>
     <row r="310">
@@ -10582,6 +10761,11 @@
       <c r="K310" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L310" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10661,13 +10845,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313"/>
     <row r="314">
@@ -10712,6 +10889,11 @@
       <c r="K314" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L314" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10791,13 +10973,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317"/>
     <row r="318">
@@ -10842,6 +11017,11 @@
       <c r="K318" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L318" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10921,13 +11101,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321"/>
     <row r="322">
@@ -10972,6 +11145,11 @@
       <c r="K322" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L322" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11051,13 +11229,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325"/>
     <row r="326">
@@ -11102,6 +11273,11 @@
       <c r="K326" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L326" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11181,13 +11357,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329"/>
     <row r="330">
@@ -11232,6 +11401,11 @@
       <c r="K330" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L330" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11311,13 +11485,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333"/>
     <row r="334">
@@ -11362,6 +11529,11 @@
       <c r="K334" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L334" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11441,13 +11613,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337"/>
     <row r="338">
@@ -11492,6 +11657,11 @@
       <c r="K338" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L338" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11571,13 +11741,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341"/>
     <row r="342">
@@ -11622,6 +11785,11 @@
       <c r="K342" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L342" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11701,13 +11869,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345"/>
     <row r="346">
@@ -11752,6 +11913,11 @@
       <c r="K346" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L346" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11831,13 +11997,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349"/>
     <row r="350">
@@ -11882,6 +12041,11 @@
       <c r="K350" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L350" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11966,12 +12130,19 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr">
+        <is>
+          <r>
+            <t>S150A</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>33</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="353"/>
     <row r="354">
@@ -12016,6 +12187,11 @@
       <c r="K354" s="1" t="n">
         <v>321</v>
       </c>
+      <c r="L354" s="1" t="inlineStr">
+        <is>
+          <t>Mutations</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12095,13 +12271,6 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
@@ -12127,19 +12127,19 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
           <r>
-            <t>S150A</t>
+            <t>S150L</t>
           </r>
           <r>
             <rPr>
               <vertAlign val="subscript"/>
             </rPr>
-            <t>33</t>
+            <t>50</t>
           </r>
         </is>
       </c>

--- a/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
+++ b/Reference_seqs/HCV_Subtype_Ref_vs_Comet_Subtype_Consensus_Aligned_NS5B.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RAS comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAS comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
